--- a/docs/sample-output/03-select-service-hotel/proforma.xlsx
+++ b/docs/sample-output/03-select-service-hotel/proforma.xlsx
@@ -270,7 +270,7 @@
     <t>Leverage Impact</t>
   </si>
   <si>
-    <t>Optimal holding period: Year 5 at 6.10% equity IRR. Leverage is positive when the equity IRR exceeds the property IRR.</t>
+    <t>Optimal holding period: Year 5 at 6.23% equity IRR. Leverage is positive when the equity IRR exceeds the property IRR.</t>
   </si>
   <si>
     <t>Acquisition-Price Sensitivity   ·   Harbor Point — select-service hotel · 5-Year Before-Tax</t>
@@ -1070,7 +1070,7 @@
         <v>19</v>
       </c>
       <c r="B14" s="7">
-        <v>30663373.6</v>
+        <v>30605902.91</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1078,7 +1078,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="8">
-        <v>0.07212451013544054</v>
+        <v>0.0722599430084907</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -1086,7 +1086,7 @@
         <v>21</v>
       </c>
       <c r="B16" s="7">
-        <v>10931492.6884</v>
+        <v>10911004.387415</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -1102,7 +1102,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="8">
-        <v>0.061047779737680344</v>
+        <v>0.062317180866599695</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -1110,7 +1110,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="9">
-        <v>1.3055584735812542</v>
+        <v>1.3124975994183088</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -1126,7 +1126,7 @@
         <v>26</v>
       </c>
       <c r="B21" s="8">
-        <v>0.061047779737680344</v>
+        <v>0.062317180866599695</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -1141,7 +1141,7 @@
         <v>28</v>
       </c>
       <c r="B23" s="7">
-        <v>30663373.6</v>
+        <v>30605902.91</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -1157,7 +1157,7 @@
         <v>30</v>
       </c>
       <c r="B25" s="7">
-        <v>199311.9284</v>
+        <v>198938.368915</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -1165,7 +1165,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="7">
-        <v>30663373.6</v>
+        <v>30605902.91</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -1173,7 +1173,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="7">
-        <v>-19931192.84</v>
+        <v>-19893836.8915</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -1181,7 +1181,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="11">
-        <v>10931492.6884</v>
+        <v>10911004.387415</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -1189,7 +1189,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="12">
-        <v>3.863832358870968</v>
+        <v>3.8565905884576615</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -1197,7 +1197,7 @@
         <v>35</v>
       </c>
       <c r="B30" s="13">
-        <v>398.8472112382935</v>
+        <v>398.09967364724247</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -1205,7 +1205,7 @@
         <v>36</v>
       </c>
       <c r="B31" s="7">
-        <v>247285.27096774193</v>
+        <v>246821.79766129033</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -1220,7 +1220,7 @@
         <v>38</v>
       </c>
       <c r="B33" s="7">
-        <v>19931192.84</v>
+        <v>19893836.8915</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -1252,7 +1252,7 @@
         <v>44</v>
       </c>
       <c r="B37" s="13">
-        <v>134576.8413976884</v>
+        <v>134324.61135822706</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -1260,7 +1260,7 @@
         <v>45</v>
       </c>
       <c r="B38" s="7">
-        <v>1614922.096772261</v>
+        <v>1611895.3362987246</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -1268,7 +1268,7 @@
         <v>46</v>
       </c>
       <c r="B39" s="8">
-        <v>0.6499999999999999</v>
+        <v>0.65</v>
       </c>
     </row>
   </sheetData>
@@ -1495,19 +1495,19 @@
         <v>62</v>
       </c>
       <c r="B13" s="17">
-        <v>-1614922.096772261</v>
+        <v>-1611895.3362987246</v>
       </c>
       <c r="C13" s="17">
-        <v>-1614922.096772261</v>
+        <v>-1611895.3362987246</v>
       </c>
       <c r="D13" s="17">
-        <v>-1614922.096772261</v>
+        <v>-1611895.3362987246</v>
       </c>
       <c r="E13" s="17">
-        <v>-1614922.096772261</v>
+        <v>-1611895.3362987246</v>
       </c>
       <c r="F13" s="17">
-        <v>-1614922.096772261</v>
+        <v>-1611895.3362987246</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1515,19 +1515,19 @@
         <v>63</v>
       </c>
       <c r="B14" s="19">
-        <v>596658.7032277388</v>
+        <v>599685.4637012752</v>
       </c>
       <c r="C14" s="19">
-        <v>663006.127227739</v>
+        <v>666032.8877012753</v>
       </c>
       <c r="D14" s="19">
-        <v>731343.9739477392</v>
+        <v>734370.7344212756</v>
       </c>
       <c r="E14" s="19">
-        <v>801731.9560693391</v>
+        <v>804758.7165428754</v>
       </c>
       <c r="F14" s="19">
-        <v>874231.5776545871</v>
+        <v>877258.3381281234</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1671,19 +1671,19 @@
         <v>70</v>
       </c>
       <c r="B9" s="17">
-        <v>-19602109.065412033</v>
+        <v>-19565369.90069584</v>
       </c>
       <c r="C9" s="17">
-        <v>-19250985.940975923</v>
+        <v>-19214904.867195833</v>
       </c>
       <c r="D9" s="17">
-        <v>-18876347.45061541</v>
+        <v>-18840968.54134019</v>
       </c>
       <c r="E9" s="17">
-        <v>-18476618.726724014</v>
+        <v>-18441989.00721097</v>
       </c>
       <c r="F9" s="17">
-        <v>-18050119.429895</v>
+        <v>-18016289.074770004</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1691,19 +1691,19 @@
         <v>71</v>
       </c>
       <c r="B10" s="19">
-        <v>5856940.934587967</v>
+        <v>5893680.099304158</v>
       </c>
       <c r="C10" s="19">
-        <v>6971864.059024077</v>
+        <v>7007945.1328041665</v>
       </c>
       <c r="D10" s="19">
-        <v>8133102.54938459</v>
+        <v>8168481.458659809</v>
       </c>
       <c r="E10" s="19">
-        <v>9343181.273275986</v>
+        <v>9377810.99278903</v>
       </c>
       <c r="F10" s="19">
-        <v>10604730.570105001</v>
+        <v>10638560.925229996</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1741,19 +1741,19 @@
         <v>73</v>
       </c>
       <c r="B13" s="22">
-        <v>0.7314492729360064</v>
+        <v>0.7300783574273608</v>
       </c>
       <c r="C13" s="22">
-        <v>0.6974236836929292</v>
+        <v>0.6961165404918246</v>
       </c>
       <c r="D13" s="22">
-        <v>0.663935403278654</v>
+        <v>0.6626910253364353</v>
       </c>
       <c r="E13" s="22">
-        <v>0.6309458655485594</v>
+        <v>0.629763318098995</v>
       </c>
       <c r="F13" s="22">
-        <v>0.5984192364783012</v>
+        <v>0.5972976519169182</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1761,19 +1761,19 @@
         <v>74</v>
       </c>
       <c r="B14" s="23">
-        <v>1.3694659354901877</v>
+        <v>1.3720374705458782</v>
       </c>
       <c r="C14" s="23">
-        <v>1.4105499135548933</v>
+        <v>1.4131985946622545</v>
       </c>
       <c r="D14" s="23">
-        <v>1.4528664109615403</v>
+        <v>1.4555945525021223</v>
       </c>
       <c r="E14" s="23">
-        <v>1.4964524032903865</v>
+        <v>1.499262389077186</v>
       </c>
       <c r="F14" s="23">
-        <v>1.5413459753890981</v>
+        <v>1.5442402607495016</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1781,19 +1781,19 @@
         <v>75</v>
       </c>
       <c r="B15" s="22">
-        <v>0.11096078482375467</v>
+        <v>0.1111691430899857</v>
       </c>
       <c r="C15" s="22">
-        <v>0.11428960836846733</v>
+        <v>0.11450421738268528</v>
       </c>
       <c r="D15" s="22">
-        <v>0.11771829661952135</v>
+        <v>0.11793934390416586</v>
       </c>
       <c r="E15" s="22">
-        <v>0.12124984551810698</v>
+        <v>0.12147752422129082</v>
       </c>
       <c r="F15" s="22">
-        <v>0.1248873408836502</v>
+        <v>0.12512184994792955</v>
       </c>
     </row>
   </sheetData>
@@ -1869,19 +1869,19 @@
         <v>77</v>
       </c>
       <c r="B5" s="22">
-        <v>0.054581631277207526</v>
+        <v>0.054961527134290776</v>
       </c>
       <c r="C5" s="22">
-        <v>0.060651015019320346</v>
+        <v>0.06104230775211609</v>
       </c>
       <c r="D5" s="22">
-        <v>0.06690248027369657</v>
+        <v>0.06730551178847619</v>
       </c>
       <c r="E5" s="22">
-        <v>0.07334148948570403</v>
+        <v>0.07375661194592703</v>
       </c>
       <c r="F5" s="22">
-        <v>0.07997366897407174</v>
+        <v>0.08040124510810143</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1889,19 +1889,19 @@
         <v>78</v>
       </c>
       <c r="B6" s="22">
-        <v>0.10187207108478609</v>
+        <v>0.10175059616352056</v>
       </c>
       <c r="C6" s="22">
-        <v>0.09509739742695825</v>
+        <v>0.09503968354198118</v>
       </c>
       <c r="D6" s="22">
-        <v>0.08992189259965473</v>
+        <v>0.08990296888569577</v>
       </c>
       <c r="E6" s="22">
-        <v>0.08580931190562559</v>
+        <v>0.08581519900131131</v>
       </c>
       <c r="F6" s="22">
-        <v>0.08243788674075961</v>
+        <v>0.08246024479191089</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1909,19 +1909,19 @@
         <v>79</v>
       </c>
       <c r="B7" s="24">
-        <v>0.5903676489363588</v>
+        <v>0.5951207911248784</v>
       </c>
       <c r="C7" s="24">
-        <v>0.7530105104689387</v>
+        <v>0.7582861476758042</v>
       </c>
       <c r="D7" s="24">
-        <v>0.9261417120583222</v>
+        <v>0.9319554995516541</v>
       </c>
       <c r="E7" s="24">
-        <v>1.1101797695594333</v>
+        <v>1.116547877957733</v>
       </c>
       <c r="F7" s="24">
-        <v>1.3055584735812542</v>
+        <v>1.3124975994183088</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1929,19 +1929,19 @@
         <v>80</v>
       </c>
       <c r="B8" s="22">
-        <v>-0.09759991966424758</v>
+        <v>-0.09590542447428582</v>
       </c>
       <c r="C8" s="22">
-        <v>0.000828288069663606</v>
+        <v>0.0018026483598889789</v>
       </c>
       <c r="D8" s="22">
-        <v>0.03593101640803399</v>
+        <v>0.03662745717160441</v>
       </c>
       <c r="E8" s="22">
-        <v>0.05389800287676244</v>
+        <v>0.054448055590641906</v>
       </c>
       <c r="F8" s="22">
-        <v>0.0647910351235717</v>
+        <v>0.06525096788714077</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1969,19 +1969,19 @@
         <v>82</v>
       </c>
       <c r="B10" s="25">
-        <v>-0.40963235106405926</v>
+        <v>-0.4048792088752594</v>
       </c>
       <c r="C10" s="25">
-        <v>-0.13654313158856188</v>
+        <v>-0.1334245976061404</v>
       </c>
       <c r="D10" s="25">
-        <v>-0.026839478348951173</v>
+        <v>-0.0246810139437669</v>
       </c>
       <c r="E10" s="25">
-        <v>0.028857744973274653</v>
+        <v>0.030467354511863113</v>
       </c>
       <c r="F10" s="25">
-        <v>0.061047779737680344</v>
+        <v>0.062317180866599695</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1989,19 +1989,19 @@
         <v>83</v>
       </c>
       <c r="B11" s="22">
-        <v>-0.312</v>
+        <v>-0.309</v>
       </c>
       <c r="C11" s="22">
-        <v>-0.1373</v>
+        <v>-0.1352</v>
       </c>
       <c r="D11" s="22">
-        <v>-0.0627</v>
+        <v>-0.0613</v>
       </c>
       <c r="E11" s="22">
-        <v>-0.025000000000000005</v>
+        <v>-0.023899999999999998</v>
       </c>
       <c r="F11" s="22">
-        <v>-0.003799999999999998</v>
+        <v>-0.0029999999999999957</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2095,19 +2095,19 @@
         <v>19</v>
       </c>
       <c r="B6" s="19">
-        <v>27597036</v>
+        <v>27545313</v>
       </c>
       <c r="C6" s="19">
-        <v>29130205</v>
+        <v>29075608</v>
       </c>
       <c r="D6" s="19">
-        <v>30663374</v>
+        <v>30605903</v>
       </c>
       <c r="E6" s="19">
-        <v>32196542</v>
+        <v>32136198</v>
       </c>
       <c r="F6" s="19">
-        <v>33729711</v>
+        <v>33666493</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2115,19 +2115,19 @@
         <v>20</v>
       </c>
       <c r="B7" s="22">
-        <v>0.08013834529186395</v>
+        <v>0.08028882445445437</v>
       </c>
       <c r="C7" s="22">
-        <v>0.07592053677617441</v>
+        <v>0.07606309728759583</v>
       </c>
       <c r="D7" s="22">
-        <v>0.07212450919458503</v>
+        <v>0.07225994279600245</v>
       </c>
       <c r="E7" s="22">
-        <v>0.06869001025016909</v>
+        <v>0.0688189934602718</v>
       </c>
       <c r="F7" s="22">
-        <v>0.06556773640900747</v>
+        <v>0.06569085767264204</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2135,19 +2135,19 @@
         <v>92</v>
       </c>
       <c r="B8" s="17">
-        <v>17938073.4</v>
+        <v>17904453.45</v>
       </c>
       <c r="C8" s="17">
-        <v>18934633.249999996</v>
+        <v>18899145.2</v>
       </c>
       <c r="D8" s="17">
-        <v>19931193.099999998</v>
+        <v>19893836.95</v>
       </c>
       <c r="E8" s="17">
-        <v>20927752.299999997</v>
+        <v>20888528.7</v>
       </c>
       <c r="F8" s="17">
-        <v>21924312.15</v>
+        <v>21883220.45</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2155,19 +2155,19 @@
         <v>21</v>
       </c>
       <c r="B9" s="17">
-        <v>9838343.334000003</v>
+        <v>9819904.0845</v>
       </c>
       <c r="C9" s="17">
-        <v>10384918.082500003</v>
+        <v>10365454.252</v>
       </c>
       <c r="D9" s="17">
-        <v>10931492.831000004</v>
+        <v>10911004.4195</v>
       </c>
       <c r="E9" s="17">
-        <v>11478067.223000001</v>
+        <v>11456554.587000001</v>
       </c>
       <c r="F9" s="17">
-        <v>12024641.971500002</v>
+        <v>12002104.754499998</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2175,19 +2175,19 @@
         <v>93</v>
       </c>
       <c r="B10" s="22">
-        <v>0.08013834529186395</v>
+        <v>0.08028882445445437</v>
       </c>
       <c r="C10" s="22">
-        <v>0.07592053677617441</v>
+        <v>0.07606309728759583</v>
       </c>
       <c r="D10" s="22">
-        <v>0.07212450919458503</v>
+        <v>0.07225994279600245</v>
       </c>
       <c r="E10" s="22">
-        <v>0.06869001025016909</v>
+        <v>0.0688189934602718</v>
       </c>
       <c r="F10" s="22">
-        <v>0.06556773640900747</v>
+        <v>0.06569085767264204</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2195,19 +2195,19 @@
         <v>94</v>
       </c>
       <c r="B11" s="22">
-        <v>0.08254249565061987</v>
+        <v>0.082697489188088</v>
       </c>
       <c r="C11" s="22">
-        <v>0.07819815287945965</v>
+        <v>0.07834499020622372</v>
       </c>
       <c r="D11" s="22">
-        <v>0.07428824447042259</v>
+        <v>0.07442774107988252</v>
       </c>
       <c r="E11" s="22">
-        <v>0.07075071055767418</v>
+        <v>0.07088356326407996</v>
       </c>
       <c r="F11" s="22">
-        <v>0.0675347685012777</v>
+        <v>0.06766158340282132</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2215,19 +2215,19 @@
         <v>95</v>
       </c>
       <c r="B12" s="22">
-        <v>0.08501877052013847</v>
+        <v>0.08517841386373065</v>
       </c>
       <c r="C12" s="22">
-        <v>0.08054409746584346</v>
+        <v>0.08069533991241043</v>
       </c>
       <c r="D12" s="22">
-        <v>0.07651689180453528</v>
+        <v>0.07666057331227902</v>
       </c>
       <c r="E12" s="22">
-        <v>0.0728732318744044</v>
+        <v>0.07301007016200237</v>
       </c>
       <c r="F12" s="22">
-        <v>0.06956081155631604</v>
+        <v>0.06969143090490595</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2235,19 +2235,19 @@
         <v>96</v>
       </c>
       <c r="B13" s="22">
-        <v>0.08756933363574262</v>
+        <v>0.08773376627964256</v>
       </c>
       <c r="C13" s="22">
-        <v>0.08296042038981875</v>
+        <v>0.08311620010978274</v>
       </c>
       <c r="D13" s="22">
-        <v>0.07881239855867134</v>
+        <v>0.07896039051164738</v>
       </c>
       <c r="E13" s="22">
-        <v>0.07505942883063653</v>
+        <v>0.07520037226686244</v>
       </c>
       <c r="F13" s="22">
-        <v>0.07164763590300552</v>
+        <v>0.07178217383205314</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2255,19 +2255,19 @@
         <v>97</v>
       </c>
       <c r="B14" s="22">
-        <v>0.0901964136448149</v>
+        <v>0.09036577926803184</v>
       </c>
       <c r="C14" s="22">
-        <v>0.08544923300151332</v>
+        <v>0.08560968611307623</v>
       </c>
       <c r="D14" s="22">
-        <v>0.08117677051543147</v>
+        <v>0.0813292022269968</v>
       </c>
       <c r="E14" s="22">
-        <v>0.07731121169555563</v>
+        <v>0.07745638343486831</v>
       </c>
       <c r="F14" s="22">
-        <v>0.07379706498009568</v>
+        <v>0.07393563904701472</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2275,19 +2275,19 @@
         <v>98</v>
       </c>
       <c r="B15" s="22">
-        <v>0.07706083227699269</v>
+        <v>0.077482933714834</v>
       </c>
       <c r="C15" s="22">
-        <v>0.06522967234518476</v>
+        <v>0.06562956157778344</v>
       </c>
       <c r="D15" s="22">
-        <v>0.05458162863806168</v>
+        <v>0.05496152653825075</v>
       </c>
       <c r="E15" s="22">
-        <v>0.04494769050505767</v>
+        <v>0.04530949474096985</v>
       </c>
       <c r="F15" s="22">
-        <v>0.03618955911329992</v>
+        <v>0.03653492030161571</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2295,19 +2295,19 @@
         <v>99</v>
       </c>
       <c r="B16" s="22">
-        <v>0.08380459204909907</v>
+        <v>0.08423935653007562</v>
       </c>
       <c r="C16" s="22">
-        <v>0.0716184973193369</v>
+        <v>0.07203038322891353</v>
       </c>
       <c r="D16" s="22">
-        <v>0.06065101230100012</v>
+        <v>0.06104230713819487</v>
       </c>
       <c r="E16" s="22">
-        <v>0.050728056024005985</v>
+        <v>0.05110071438699553</v>
       </c>
       <c r="F16" s="22">
-        <v>0.04170718069049551</v>
+        <v>0.042062902714460775</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -2315,19 +2315,19 @@
         <v>100</v>
       </c>
       <c r="B17" s="22">
-        <v>0.09075066461436865</v>
+        <v>0.09119847202977449</v>
       </c>
       <c r="C17" s="22">
-        <v>0.07819898704271361</v>
+        <v>0.07862322952957754</v>
       </c>
       <c r="D17" s="22">
-        <v>0.06690247747382673</v>
+        <v>0.06730551115613732</v>
       </c>
       <c r="E17" s="22">
-        <v>0.05668183250852277</v>
+        <v>0.057065670622402004</v>
       </c>
       <c r="F17" s="22">
-        <v>0.04739033091500698</v>
+        <v>0.0477567245996912</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -2335,19 +2335,19 @@
         <v>101</v>
       </c>
       <c r="B18" s="22">
-        <v>0.09790511935659627</v>
+        <v>0.0983663609944643</v>
       </c>
       <c r="C18" s="22">
-        <v>0.08497689145779158</v>
+        <v>0.08541386121926144</v>
       </c>
       <c r="D18" s="22">
-        <v>0.07334148660183809</v>
+        <v>0.07375661129461801</v>
       </c>
       <c r="E18" s="22">
-        <v>0.06281422228757502</v>
+        <v>0.06320957554487062</v>
       </c>
       <c r="F18" s="22">
-        <v>0.05324397564625376</v>
+        <v>0.05362136114147851</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2355,19 +2355,19 @@
         <v>102</v>
       </c>
       <c r="B19" s="22">
-        <v>0.10527420774109074</v>
+        <v>0.10574928662809481</v>
       </c>
       <c r="C19" s="22">
-        <v>0.09195813300532191</v>
+        <v>0.09240821185963587</v>
       </c>
       <c r="D19" s="22">
-        <v>0.07997366600368983</v>
+        <v>0.08040124443725313</v>
       </c>
       <c r="E19" s="22">
-        <v>0.06913058375999885</v>
+        <v>0.06953779761501333</v>
       </c>
       <c r="F19" s="22">
-        <v>0.05927322971943795</v>
+        <v>0.05966193677951945</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2375,19 +2375,19 @@
         <v>103</v>
       </c>
       <c r="B20" s="22">
-        <v>0.0026667646482037037</v>
+        <v>0.004549514467418258</v>
       </c>
       <c r="C20" s="22">
-        <v>-0.05010518120285854</v>
+        <v>-0.04832150715475283</v>
       </c>
       <c r="D20" s="22">
-        <v>-0.09759993143618459</v>
+        <v>-0.09590542713268</v>
       </c>
       <c r="E20" s="22">
-        <v>-0.14057134458713239</v>
+        <v>-0.13895754563131024</v>
       </c>
       <c r="F20" s="22">
-        <v>-0.17963629157704414</v>
+        <v>-0.1780958355241749</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2395,19 +2395,19 @@
         <v>104</v>
       </c>
       <c r="B21" s="22">
-        <v>0.05710080386655804</v>
+        <v>0.05813194083091418</v>
       </c>
       <c r="C21" s="22">
-        <v>0.027825725762337078</v>
+        <v>0.02882730283642807</v>
       </c>
       <c r="D21" s="22">
-        <v>0.0008282812978466327</v>
+        <v>0.0018026468316778297</v>
       </c>
       <c r="E21" s="22">
-        <v>-0.024171070614600363</v>
+        <v>-0.02322187671489647</v>
       </c>
       <c r="F21" s="22">
-        <v>-0.047406234782670406</v>
+        <v>-0.04648038441530961</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2415,19 +2415,19 @@
         <v>105</v>
       </c>
       <c r="B22" s="22">
-        <v>0.07586268613921643</v>
+        <v>0.07658904120940757</v>
       </c>
       <c r="C22" s="22">
-        <v>0.055161427939564356</v>
+        <v>0.05587223975502864</v>
       </c>
       <c r="D22" s="22">
-        <v>0.0359310115672455</v>
+        <v>0.03662745607957631</v>
       </c>
       <c r="E22" s="22">
-        <v>0.017999176859269644</v>
+        <v>0.018682274415420242</v>
       </c>
       <c r="F22" s="22">
-        <v>0.0012209638213477201</v>
+        <v>0.0018916375602595634</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2435,19 +2435,19 @@
         <v>106</v>
       </c>
       <c r="B23" s="22">
-        <v>0.08534155376741312</v>
+        <v>0.08591177422065861</v>
       </c>
       <c r="C23" s="22">
-        <v>0.06906443489127248</v>
+        <v>0.06962417270746099</v>
       </c>
       <c r="D23" s="22">
-        <v>0.053897999053185944</v>
+        <v>0.05444805472805632</v>
       </c>
       <c r="E23" s="22">
-        <v>0.03971432491948247</v>
+        <v>0.04025539001809879</v>
       </c>
       <c r="F23" s="22">
-        <v>0.02640559573338404</v>
+        <v>0.026938297059510334</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2455,19 +2455,19 @@
         <v>107</v>
       </c>
       <c r="B24" s="22">
-        <v>0.09104812578972535</v>
+        <v>0.09152366272893525</v>
       </c>
       <c r="C24" s="22">
-        <v>0.07746451918762931</v>
+        <v>0.07793193572617943</v>
       </c>
       <c r="D24" s="22">
-        <v>0.06479103192629182</v>
+        <v>0.06525096716637632</v>
       </c>
       <c r="E24" s="22">
-        <v>0.052923282993432685</v>
+        <v>0.05337628657054368</v>
       </c>
       <c r="F24" s="22">
-        <v>0.041773300226554705</v>
+        <v>0.04221986930610096</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2475,19 +2475,19 @@
         <v>108</v>
       </c>
       <c r="B25" s="22">
-        <v>-0.12837937963984689</v>
+        <v>-0.12309817397582315</v>
       </c>
       <c r="C25" s="22">
-        <v>-0.27640727823998135</v>
+        <v>-0.2714039849779355</v>
       </c>
       <c r="D25" s="22">
-        <v>-0.4096323840842344</v>
+        <v>-0.40487921633298807</v>
       </c>
       <c r="E25" s="22">
-        <v>-0.5301693073689517</v>
+        <v>-0.5256425220786667</v>
       </c>
       <c r="F25" s="22">
-        <v>-0.6397484013093013</v>
+        <v>-0.6354273464622082</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2495,19 +2495,19 @@
         <v>109</v>
       </c>
       <c r="B26" s="22">
-        <v>0.03331899790304956</v>
+        <v>0.036268548178353</v>
       </c>
       <c r="C26" s="22">
-        <v>-0.05266413042043716</v>
+        <v>-0.04964445800756158</v>
       </c>
       <c r="D26" s="22">
-        <v>-0.136543153288225</v>
+        <v>-0.13342460249091015</v>
       </c>
       <c r="E26" s="22">
-        <v>-0.21938318421472955</v>
+        <v>-0.21612812122932284</v>
       </c>
       <c r="F26" s="22">
-        <v>-0.3023932400685025</v>
+        <v>-0.29894889807887126</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2515,19 +2515,19 @@
         <v>110</v>
       </c>
       <c r="B27" s="22">
-        <v>0.08914306746334286</v>
+        <v>0.09112888197034613</v>
       </c>
       <c r="C27" s="22">
-        <v>0.030835612324847054</v>
+        <v>0.03289720191404221</v>
       </c>
       <c r="D27" s="22">
-        <v>-0.02683949337227404</v>
+        <v>-0.024681017323831694</v>
       </c>
       <c r="E27" s="22">
-        <v>-0.08457212402748829</v>
+        <v>-0.08228944343220918</v>
       </c>
       <c r="F27" s="22">
-        <v>-0.1431528844778237</v>
+        <v>-0.14070880501125804</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -2535,19 +2535,19 @@
         <v>111</v>
       </c>
       <c r="B28" s="22">
-        <v>0.11539445885330979</v>
+        <v>0.11687596220969335</v>
       </c>
       <c r="C28" s="22">
-        <v>0.07188584217552055</v>
+        <v>0.0734242831258038</v>
       </c>
       <c r="D28" s="22">
-        <v>0.02885773377089875</v>
+        <v>0.030467351991022438</v>
       </c>
       <c r="E28" s="22">
-        <v>-0.014152961533191108</v>
+        <v>-0.01245436908875469</v>
       </c>
       <c r="F28" s="22">
-        <v>-0.05765496648135683</v>
+        <v>-0.05584418878180457</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2555,19 +2555,19 @@
         <v>112</v>
       </c>
       <c r="B29" s="22">
-        <v>0.12961622123054073</v>
+        <v>0.13079508775491827</v>
       </c>
       <c r="C29" s="22">
-        <v>0.09506505630234992</v>
+        <v>0.09628431411737357</v>
       </c>
       <c r="D29" s="22">
-        <v>0.06104777090374143</v>
+        <v>0.06231717887853343</v>
       </c>
       <c r="E29" s="22">
-        <v>0.027232651732448585</v>
+        <v>0.028563947479183206</v>
       </c>
       <c r="F29" s="22">
-        <v>-0.006726273242174365</v>
+        <v>-0.005318412340504907</v>
       </c>
     </row>
   </sheetData>
